--- a/data/reg_dif_med_results/difmedias_entre_anos_2019x2023.xlsx
+++ b/data/reg_dif_med_results/difmedias_entre_anos_2019x2023.xlsx
@@ -210,10 +210,10 @@
     <t>15652</t>
   </si>
   <si>
-    <t>20668</t>
-  </si>
-  <si>
-    <t>20664</t>
+    <t>20669</t>
+  </si>
+  <si>
+    <t>20665</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -231,7 +231,7 @@
     <t>(0.009)</t>
   </si>
   <si>
-    <t>38.979</t>
+    <t>38.980</t>
   </si>
   <si>
     <t>(0.092)</t>
@@ -516,13 +516,13 @@
     <t>32403</t>
   </si>
   <si>
-    <t>38289</t>
-  </si>
-  <si>
-    <t>34189</t>
-  </si>
-  <si>
-    <t>38285</t>
+    <t>38290</t>
+  </si>
+  <si>
+    <t>34190</t>
+  </si>
+  <si>
+    <t>38286</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -534,10 +534,10 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.106***</t>
-  </si>
-  <si>
-    <t>0.341</t>
+    <t>0.107***</t>
+  </si>
+  <si>
+    <t>0.340</t>
   </si>
   <si>
     <t>-0.006***</t>
@@ -648,7 +648,7 @@
     <t>0.038***</t>
   </si>
   <si>
-    <t>-0.146***</t>
+    <t>-0.145***</t>
   </si>
   <si>
     <t>0.008***</t>
